--- a/loi_darcy.xlsx
+++ b/loi_darcy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673B95D5-CEE3-4B52-8F22-34BE5EDA4057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ABBA45-F481-4F33-B70B-4A86A9FEED7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AE20"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.5546875" customWidth="1"/>
@@ -446,7 +446,7 @@
     <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="9.109375" customWidth="1"/>
     <col min="18" max="18" width="2.109375" customWidth="1"/>
-    <col min="19" max="19" width="11.77734375" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" customWidth="1"/>
     <col min="20" max="20" width="10.109375" customWidth="1"/>
     <col min="21" max="21" width="14.88671875" customWidth="1"/>
     <col min="22" max="22" width="8.33203125" customWidth="1"/>
@@ -461,125 +461,218 @@
     <col min="31" max="31" width="9.5546875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="U1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="2" spans="1:31" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>30.2</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="F2">
+        <v>198</v>
+      </c>
+      <c r="G2">
+        <v>273.5</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <f t="shared" ref="I2:I15" si="0">G2-F2</f>
+        <v>75.5</v>
+      </c>
+      <c r="J2">
+        <f t="shared" ref="J2:J15" si="1">2*H2</f>
         <v>1</v>
       </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
-      </c>
-      <c r="P2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="L2">
+        <v>1138</v>
+      </c>
+      <c r="M2">
+        <v>993</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" ref="P2:P15" si="2">L2-M2</f>
+        <v>145</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" ref="Q2:Q15" si="3">O2+N2</f>
         <v>4</v>
       </c>
-      <c r="U2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="W2" t="s">
-        <v>6</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>14</v>
+      <c r="S2">
+        <f t="shared" ref="S2:S15" si="4">(I2/10^3)/($AD$2*C2)</f>
+        <v>2.5050100200400804E-6</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ref="T2:T15" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
+        <v>3.4292054268838759E-8</v>
+      </c>
+      <c r="U2">
+        <f t="shared" ref="U2:U15" si="6">S2/($Z$2/10^6)</f>
+        <v>5.964309571524001E-4</v>
+      </c>
+      <c r="V2">
+        <f t="shared" ref="V2:V15" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
+        <v>1.6380612974879218E-5</v>
+      </c>
+      <c r="W2">
+        <f t="shared" ref="W2:W15" si="8">P2/$AB$2</f>
+        <v>0.4380664652567976</v>
+      </c>
+      <c r="X2">
+        <f t="shared" ref="X2:X15" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
+        <v>1.2102696241490761E-2</v>
+      </c>
+      <c r="Z2">
+        <v>4200</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>331</v>
+      </c>
+      <c r="AC2">
+        <v>0.5</v>
+      </c>
+      <c r="AD2">
+        <v>998</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0.1</v>
       </c>
       <c r="F3">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="G3">
-        <v>273.5</v>
+        <v>299.5</v>
       </c>
       <c r="H3">
         <v>0.5</v>
       </c>
       <c r="I3">
-        <f>G3-F3</f>
-        <v>75.5</v>
+        <f t="shared" si="0"/>
+        <v>102</v>
       </c>
       <c r="J3">
-        <f>2*H3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1138</v>
+        <v>1115</v>
       </c>
       <c r="M3">
-        <v>993</v>
+        <v>932</v>
       </c>
       <c r="N3">
         <v>2</v>
@@ -588,91 +681,73 @@
         <v>2</v>
       </c>
       <c r="P3">
-        <f>L3-M3</f>
-        <v>145</v>
+        <f t="shared" si="2"/>
+        <v>183</v>
       </c>
       <c r="Q3">
-        <f>O3+N3</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S3">
-        <f>(I3/10^3)/($AD$3*C3)</f>
-        <v>2.5050100200400804E-6</v>
+        <f t="shared" si="4"/>
+        <v>3.406813627254509E-6</v>
       </c>
       <c r="T3">
-        <f>S3*SQRT((J3/I3)^2+(D3/C3)^2+($AE$3/$AD$3)^2)</f>
-        <v>3.4292054268838759E-8</v>
+        <f t="shared" si="5"/>
+        <v>3.5442652785390082E-8</v>
       </c>
       <c r="U3">
-        <f>S3/($Z$3/10^6)</f>
-        <v>5.964309571524001E-4</v>
+        <f t="shared" si="6"/>
+        <v>8.1114610172726409E-4</v>
       </c>
       <c r="V3">
-        <f>U3*SQRT((T3/S3)^2+($AA$3/$Z$3)^2)</f>
-        <v>1.6380612974879218E-5</v>
+        <f t="shared" si="7"/>
+        <v>2.1076151770803291E-5</v>
       </c>
       <c r="W3">
-        <f>P3/$AB$3</f>
-        <v>0.4380664652567976</v>
+        <f t="shared" si="8"/>
+        <v>0.55287009063444104</v>
       </c>
       <c r="X3">
-        <f>W3*SQRT((Q3/P3)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2102696241490761E-2</v>
-      </c>
-      <c r="Z3">
-        <v>4200</v>
-      </c>
-      <c r="AA3">
-        <v>100</v>
-      </c>
-      <c r="AB3">
-        <v>331</v>
-      </c>
-      <c r="AC3">
-        <v>0.5</v>
-      </c>
-      <c r="AD3">
-        <v>998</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>1.2113415902573529E-2</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D4">
         <v>0.1</v>
       </c>
       <c r="F4">
-        <v>197.5</v>
+        <v>198</v>
       </c>
       <c r="G4">
-        <v>299.5</v>
+        <v>321</v>
       </c>
       <c r="H4">
         <v>0.5</v>
       </c>
       <c r="I4">
-        <f>G4-F4</f>
-        <v>102</v>
+        <f t="shared" si="0"/>
+        <v>123</v>
       </c>
       <c r="J4">
-        <f>2*H4</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L4">
         <v>1115</v>
       </c>
       <c r="M4">
-        <v>932</v>
+        <v>889</v>
       </c>
       <c r="N4">
         <v>2</v>
@@ -681,47 +756,47 @@
         <v>2</v>
       </c>
       <c r="P4">
-        <f>L4-M4</f>
-        <v>183</v>
+        <f t="shared" si="2"/>
+        <v>226</v>
       </c>
       <c r="Q4">
-        <f>O4+N4</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S4">
-        <f>(I4/10^3)/($AD$3*C4)</f>
-        <v>3.406813627254509E-6</v>
+        <f t="shared" si="4"/>
+        <v>4.121956287156253E-6</v>
       </c>
       <c r="T4">
-        <f>S4*SQRT((J4/I4)^2+(D4/C4)^2+($AE$3/$AD$3)^2)</f>
-        <v>3.5442652785390082E-8</v>
+        <f t="shared" si="5"/>
+        <v>3.6471229298589113E-8</v>
       </c>
       <c r="U4">
-        <f>S4/($Z$3/10^6)</f>
-        <v>8.1114610172726409E-4</v>
+        <f t="shared" si="6"/>
+        <v>9.8141816360863181E-4</v>
       </c>
       <c r="V4">
-        <f>U4*SQRT((T4/S4)^2+($AA$3/$Z$3)^2)</f>
-        <v>2.1076151770803291E-5</v>
+        <f t="shared" si="7"/>
+        <v>2.4928431214823366E-5</v>
       </c>
       <c r="W4">
-        <f>P4/$AB$3</f>
-        <v>0.55287009063444104</v>
+        <f t="shared" si="8"/>
+        <v>0.68277945619335345</v>
       </c>
       <c r="X4">
-        <f>W4*SQRT((Q4/P4)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2113415902573529E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2128525482848011E-2</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>0.1</v>
@@ -730,24 +805,24 @@
         <v>198</v>
       </c>
       <c r="G5">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="H5">
         <v>0.5</v>
       </c>
       <c r="I5">
-        <f>G5-F5</f>
-        <v>123</v>
+        <f t="shared" si="0"/>
+        <v>142</v>
       </c>
       <c r="J5">
-        <f>2*H5</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1115</v>
+        <v>1094</v>
       </c>
       <c r="M5">
-        <v>889</v>
+        <v>839</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -756,73 +831,73 @@
         <v>2</v>
       </c>
       <c r="P5">
-        <f>L5-M5</f>
-        <v>226</v>
+        <f t="shared" si="2"/>
+        <v>255</v>
       </c>
       <c r="Q5">
-        <f>O5+N5</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S5">
-        <f>(I5/10^3)/($AD$3*C5)</f>
-        <v>4.121956287156253E-6</v>
+        <f t="shared" si="4"/>
+        <v>4.7428189712758846E-6</v>
       </c>
       <c r="T5">
-        <f>S5*SQRT((J5/I5)^2+(D5/C5)^2+($AE$3/$AD$3)^2)</f>
-        <v>3.6471229298589113E-8</v>
+        <f t="shared" si="5"/>
+        <v>3.7257086899611824E-8</v>
       </c>
       <c r="U5">
-        <f>S5/($Z$3/10^6)</f>
-        <v>9.8141816360863181E-4</v>
+        <f t="shared" si="6"/>
+        <v>1.129242612208544E-3</v>
       </c>
       <c r="V5">
-        <f>U5*SQRT((T5/S5)^2+($AA$3/$Z$3)^2)</f>
-        <v>2.4928431214823366E-5</v>
+        <f t="shared" si="7"/>
+        <v>2.8312296408463423E-5</v>
       </c>
       <c r="W5">
-        <f>P5/$AB$3</f>
-        <v>0.68277945619335345</v>
+        <f t="shared" si="8"/>
+        <v>0.77039274924471302</v>
       </c>
       <c r="X5">
-        <f>W5*SQRT((Q5/P5)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2128525482848011E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2140496163327807E-2</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="D6">
         <v>0.1</v>
       </c>
       <c r="F6">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="G6">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="H6">
         <v>0.5</v>
       </c>
       <c r="I6">
-        <f>G6-F6</f>
-        <v>142</v>
+        <f t="shared" si="0"/>
+        <v>160.5</v>
       </c>
       <c r="J6">
-        <f>2*H6</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="M6">
-        <v>839</v>
+        <v>791</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -831,44 +906,44 @@
         <v>2</v>
       </c>
       <c r="P6">
-        <f>L6-M6</f>
-        <v>255</v>
+        <f t="shared" si="2"/>
+        <v>292</v>
       </c>
       <c r="Q6">
-        <f>O6+N6</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S6">
-        <f>(I6/10^3)/($AD$3*C6)</f>
-        <v>4.7428189712758846E-6</v>
+        <f t="shared" si="4"/>
+        <v>5.3429117370954528E-6</v>
       </c>
       <c r="T6">
-        <f>S6*SQRT((J6/I6)^2+(D6/C6)^2+($AE$3/$AD$3)^2)</f>
-        <v>3.7257086899611824E-8</v>
+        <f t="shared" si="5"/>
+        <v>3.810395820831726E-8</v>
       </c>
       <c r="U6">
-        <f>S6/($Z$3/10^6)</f>
-        <v>1.129242612208544E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.272121842165584E-3</v>
       </c>
       <c r="V6">
-        <f>U6*SQRT((T6/S6)^2+($AA$3/$Z$3)^2)</f>
-        <v>2.8312296408463423E-5</v>
+        <f t="shared" si="7"/>
+        <v>3.1618161422865852E-5</v>
       </c>
       <c r="W6">
-        <f>P6/$AB$3</f>
-        <v>0.77039274924471302</v>
+        <f t="shared" si="8"/>
+        <v>0.8821752265861027</v>
       </c>
       <c r="X6">
-        <f>W6*SQRT((Q6/P6)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2140496163327807E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.215784380647268E-2</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>30.1</v>
@@ -877,73 +952,73 @@
         <v>0.1</v>
       </c>
       <c r="F7">
-        <v>197.5</v>
+        <v>198.5</v>
       </c>
       <c r="G7">
-        <v>358</v>
+        <v>397.5</v>
       </c>
       <c r="H7">
         <v>0.5</v>
       </c>
       <c r="I7">
-        <f>G7-F7</f>
-        <v>160.5</v>
+        <f t="shared" si="0"/>
+        <v>199</v>
       </c>
       <c r="J7">
-        <f>2*H7</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1083</v>
+        <v>1060</v>
       </c>
       <c r="M7">
-        <v>791</v>
+        <v>694</v>
       </c>
       <c r="N7">
         <v>2</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <f>L7-M7</f>
-        <v>292</v>
+        <f t="shared" si="2"/>
+        <v>366</v>
       </c>
       <c r="Q7">
-        <f>O7+N7</f>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="S7">
-        <f>(I7/10^3)/($AD$3*C7)</f>
-        <v>5.3429117370954528E-6</v>
+        <f t="shared" si="4"/>
+        <v>6.6245447706043312E-6</v>
       </c>
       <c r="T7">
-        <f>S7*SQRT((J7/I7)^2+(D7/C7)^2+($AE$3/$AD$3)^2)</f>
-        <v>3.810395820831726E-8</v>
+        <f t="shared" si="5"/>
+        <v>4.0454932254959881E-8</v>
       </c>
       <c r="U7">
-        <f>S7/($Z$3/10^6)</f>
-        <v>1.272121842165584E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.5772725644296027E-3</v>
       </c>
       <c r="V7">
-        <f>U7*SQRT((T7/S7)^2+($AA$3/$Z$3)^2)</f>
-        <v>3.1618161422865852E-5</v>
+        <f t="shared" si="7"/>
+        <v>3.8769691046076259E-5</v>
       </c>
       <c r="W7">
-        <f>P7/$AB$3</f>
-        <v>0.8821752265861027</v>
+        <f t="shared" si="8"/>
+        <v>1.1057401812688821</v>
       </c>
       <c r="X7">
-        <f>W7*SQRT((Q7/P7)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.215784380647268E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.8203680576191282E-2</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>30.1</v>
@@ -952,226 +1027,226 @@
         <v>0.1</v>
       </c>
       <c r="F8">
-        <v>198.5</v>
+        <v>198</v>
       </c>
       <c r="G8">
-        <v>397.5</v>
+        <v>420</v>
       </c>
       <c r="H8">
         <v>0.5</v>
       </c>
       <c r="I8">
-        <f>G8-F8</f>
-        <v>199</v>
+        <f t="shared" si="0"/>
+        <v>222</v>
       </c>
       <c r="J8">
-        <f>2*H8</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="M8">
-        <v>694</v>
+        <v>486</v>
       </c>
       <c r="N8">
         <v>2</v>
       </c>
       <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="2"/>
+        <v>562</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="P8">
-        <f>L8-M8</f>
-        <v>366</v>
-      </c>
-      <c r="Q8">
-        <f>O8+N8</f>
-        <v>6</v>
-      </c>
       <c r="S8">
-        <f>(I8/10^3)/($AD$3*C8)</f>
-        <v>6.6245447706043312E-6</v>
+        <f t="shared" si="4"/>
+        <v>7.3901956737395054E-6</v>
       </c>
       <c r="T8">
-        <f>S8*SQRT((J8/I8)^2+(D8/C8)^2+($AE$3/$AD$3)^2)</f>
-        <v>4.0454932254959881E-8</v>
+        <f t="shared" si="5"/>
+        <v>4.2021551106583754E-8</v>
       </c>
       <c r="U8">
-        <f>S8/($Z$3/10^6)</f>
-        <v>1.5772725644296027E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.759570398509406E-3</v>
       </c>
       <c r="V8">
-        <f>U8*SQRT((T8/S8)^2+($AA$3/$Z$3)^2)</f>
-        <v>3.8769691046076259E-5</v>
+        <f t="shared" si="7"/>
+        <v>4.307266616881891E-5</v>
       </c>
       <c r="W8">
-        <f>P8/$AB$3</f>
-        <v>1.1057401812688821</v>
+        <f t="shared" si="8"/>
+        <v>1.6978851963746224</v>
       </c>
       <c r="X8">
-        <f>W8*SQRT((Q8/P8)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.8203680576191282E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2353763403938013E-2</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D9">
         <v>0.1</v>
       </c>
       <c r="F9">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G9">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="H9">
         <v>0.5</v>
       </c>
       <c r="I9">
-        <f>G9-F9</f>
-        <v>222</v>
+        <f t="shared" si="0"/>
+        <v>239</v>
       </c>
       <c r="J9">
-        <f>2*H9</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="M9">
-        <v>486</v>
+        <v>600</v>
       </c>
       <c r="N9">
         <v>2</v>
       </c>
       <c r="O9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P9">
-        <f>L9-M9</f>
-        <v>562</v>
+        <f t="shared" si="2"/>
+        <v>440</v>
       </c>
       <c r="Q9">
-        <f>O9+N9</f>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="S9">
-        <f>(I9/10^3)/($AD$3*C9)</f>
-        <v>7.3901956737395054E-6</v>
+        <f t="shared" si="4"/>
+        <v>8.0093296961816622E-6</v>
       </c>
       <c r="T9">
-        <f>S9*SQRT((J9/I9)^2+(D9/C9)^2+($AE$3/$AD$3)^2)</f>
-        <v>4.2021551106583754E-8</v>
+        <f t="shared" si="5"/>
+        <v>4.364626552580502E-8</v>
       </c>
       <c r="U9">
-        <f>S9/($Z$3/10^6)</f>
-        <v>1.759570398509406E-3</v>
+        <f t="shared" si="6"/>
+        <v>1.9069832609956339E-3</v>
       </c>
       <c r="V9">
-        <f>U9*SQRT((T9/S9)^2+($AA$3/$Z$3)^2)</f>
-        <v>4.307266616881891E-5</v>
+        <f t="shared" si="7"/>
+        <v>4.6578420007594534E-5</v>
       </c>
       <c r="W9">
-        <f>P9/$AB$3</f>
-        <v>1.6978851963746224</v>
+        <f t="shared" si="8"/>
+        <v>1.3293051359516617</v>
       </c>
       <c r="X9">
-        <f>W9*SQRT((Q9/P9)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2353763403938013E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.5238618895658656E-2</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
       <c r="F10">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G10">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="H10">
         <v>0.5</v>
       </c>
       <c r="I10">
-        <f>G10-F10</f>
-        <v>239</v>
+        <f t="shared" si="0"/>
+        <v>263</v>
       </c>
       <c r="J10">
-        <f>2*H10</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L10">
-        <v>1040</v>
+        <v>1016</v>
       </c>
       <c r="M10">
-        <v>600</v>
+        <v>380</v>
       </c>
       <c r="N10">
         <v>2</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10">
-        <f>L10-M10</f>
-        <v>440</v>
+        <f t="shared" si="2"/>
+        <v>636</v>
       </c>
       <c r="Q10">
-        <f>O10+N10</f>
-        <v>5</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="S10">
-        <f>(I10/10^3)/($AD$3*C10)</f>
-        <v>8.0093296961816622E-6</v>
+        <f t="shared" si="4"/>
+        <v>8.7842351369405489E-6</v>
       </c>
       <c r="T10">
-        <f>S10*SQRT((J10/I10)^2+(D10/C10)^2+($AE$3/$AD$3)^2)</f>
-        <v>4.364626552580502E-8</v>
+        <f t="shared" si="5"/>
+        <v>4.5281404465810625E-8</v>
       </c>
       <c r="U10">
-        <f>S10/($Z$3/10^6)</f>
-        <v>1.9069832609956339E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.0914845564144165E-3</v>
       </c>
       <c r="V10">
-        <f>U10*SQRT((T10/S10)^2+($AA$3/$Z$3)^2)</f>
-        <v>4.6578420007594534E-5</v>
+        <f t="shared" si="7"/>
+        <v>5.0950980225292664E-5</v>
       </c>
       <c r="W10">
-        <f>P10/$AB$3</f>
-        <v>1.3293051359516617</v>
+        <f t="shared" si="8"/>
+        <v>1.9214501510574018</v>
       </c>
       <c r="X10">
-        <f>W10*SQRT((Q10/P10)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.5238618895658656E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.242826741913804E-2</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D11">
         <v>0.1</v>
@@ -1180,212 +1255,212 @@
         <v>198</v>
       </c>
       <c r="G11">
-        <v>461</v>
+        <v>502.5</v>
       </c>
       <c r="H11">
         <v>0.5</v>
       </c>
       <c r="I11">
-        <f>G11-F11</f>
-        <v>263</v>
+        <f t="shared" si="0"/>
+        <v>304.5</v>
       </c>
       <c r="J11">
-        <f>2*H11</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L11">
-        <v>1016</v>
+        <v>980</v>
       </c>
       <c r="M11">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <f>L11-M11</f>
-        <v>636</v>
+        <f t="shared" si="2"/>
+        <v>576</v>
       </c>
       <c r="Q11">
-        <f>O11+N11</f>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="S11">
-        <f>(I11/10^3)/($AD$3*C11)</f>
-        <v>8.7842351369405489E-6</v>
+        <f t="shared" si="4"/>
+        <v>1.0204355198691699E-5</v>
       </c>
       <c r="T11">
-        <f>S11*SQRT((J11/I11)^2+(D11/C11)^2+($AE$3/$AD$3)^2)</f>
-        <v>4.5281404465810625E-8</v>
+        <f t="shared" si="5"/>
+        <v>4.8911444595405938E-8</v>
       </c>
       <c r="U11">
-        <f>S11/($Z$3/10^6)</f>
-        <v>2.0914845564144165E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.4296083806408806E-3</v>
       </c>
       <c r="V11">
-        <f>U11*SQRT((T11/S11)^2+($AA$3/$Z$3)^2)</f>
-        <v>5.0950980225292664E-5</v>
+        <f t="shared" si="7"/>
+        <v>5.9008386661903181E-5</v>
       </c>
       <c r="W11">
-        <f>P11/$AB$3</f>
-        <v>1.9214501510574018</v>
+        <f t="shared" si="8"/>
+        <v>1.7401812688821752</v>
       </c>
       <c r="X11">
-        <f>W11*SQRT((Q11/P11)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.242826741913804E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.4311712998973202E-2</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>29.9</v>
+        <v>30.4</v>
       </c>
       <c r="D12">
         <v>0.1</v>
       </c>
       <c r="F12">
-        <v>198</v>
+        <v>197.5</v>
       </c>
       <c r="G12">
-        <v>502.5</v>
+        <v>536.5</v>
       </c>
       <c r="H12">
         <v>0.5</v>
       </c>
       <c r="I12">
-        <f>G12-F12</f>
-        <v>304.5</v>
+        <f t="shared" si="0"/>
+        <v>339</v>
       </c>
       <c r="J12">
-        <f>2*H12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L12">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="M12">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="O12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <f>L12-M12</f>
-        <v>576</v>
+        <f t="shared" si="2"/>
+        <v>596</v>
       </c>
       <c r="Q12">
-        <f>O12+N12</f>
-        <v>8</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="S12">
-        <f>(I12/10^3)/($AD$3*C12)</f>
-        <v>1.0204355198691699E-5</v>
+        <f t="shared" si="4"/>
+        <v>1.1173663115705097E-5</v>
       </c>
       <c r="T12">
-        <f>S12*SQRT((J12/I12)^2+(D12/C12)^2+($AE$3/$AD$3)^2)</f>
-        <v>4.8911444595405938E-8</v>
+        <f t="shared" si="5"/>
+        <v>5.0623327338103899E-8</v>
       </c>
       <c r="U12">
-        <f>S12/($Z$3/10^6)</f>
-        <v>2.4296083806408806E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.6603959799297852E-3</v>
       </c>
       <c r="V12">
-        <f>U12*SQRT((T12/S12)^2+($AA$3/$Z$3)^2)</f>
-        <v>5.9008386661903181E-5</v>
+        <f t="shared" si="7"/>
+        <v>6.4479333191259661E-5</v>
       </c>
       <c r="W12">
-        <f>P12/$AB$3</f>
-        <v>1.7401812688821752</v>
+        <f t="shared" si="8"/>
+        <v>1.8006042296072509</v>
       </c>
       <c r="X12">
-        <f>W12*SQRT((Q12/P12)^2+($AC$3/$AB$3)^2)</f>
-        <v>2.4311712998973202E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2386907336791842E-2</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0.1</v>
       </c>
       <c r="F13">
-        <v>197.5</v>
+        <v>199.5</v>
       </c>
       <c r="G13">
-        <v>536.5</v>
+        <v>576.5</v>
       </c>
       <c r="H13">
         <v>0.5</v>
       </c>
       <c r="I13">
-        <f>G13-F13</f>
-        <v>339</v>
+        <f t="shared" si="0"/>
+        <v>377</v>
       </c>
       <c r="J13">
-        <f>2*H13</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L13">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="M13">
-        <v>380</v>
+        <v>174</v>
       </c>
       <c r="N13">
         <v>2</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <f>L13-M13</f>
-        <v>596</v>
+        <f t="shared" si="2"/>
+        <v>752</v>
       </c>
       <c r="Q13">
-        <f>O13+N13</f>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="S13">
-        <f>(I13/10^3)/($AD$3*C13)</f>
-        <v>1.1173663115705097E-5</v>
+        <f t="shared" si="4"/>
+        <v>1.259185036740147E-5</v>
       </c>
       <c r="T13">
-        <f>S13*SQRT((J13/I13)^2+(D13/C13)^2+($AE$3/$AD$3)^2)</f>
-        <v>5.0623327338103899E-8</v>
+        <f t="shared" si="5"/>
+        <v>5.5104251991726919E-8</v>
       </c>
       <c r="U13">
-        <f>S13/($Z$3/10^6)</f>
-        <v>2.6603959799297852E-3</v>
+        <f t="shared" si="6"/>
+        <v>2.9980596112860643E-3</v>
       </c>
       <c r="V13">
-        <f>U13*SQRT((T13/S13)^2+($AA$3/$Z$3)^2)</f>
-        <v>6.4479333191259661E-5</v>
+        <f t="shared" si="7"/>
+        <v>7.2578088728497025E-5</v>
       </c>
       <c r="W13">
-        <f>P13/$AB$3</f>
-        <v>1.8006042296072509</v>
+        <f t="shared" si="8"/>
+        <v>2.2719033232628401</v>
       </c>
       <c r="X13">
-        <f>W13*SQRT((Q13/P13)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2386907336791842E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.6415849479503985E-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
@@ -1393,112 +1468,94 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="D14">
         <v>0.1</v>
       </c>
       <c r="F14">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="G14">
-        <v>576.5</v>
+        <v>574</v>
       </c>
       <c r="H14">
         <v>0.5</v>
       </c>
       <c r="I14">
-        <f>G14-F14</f>
-        <v>377</v>
+        <f t="shared" si="0"/>
+        <v>376</v>
       </c>
       <c r="J14">
-        <f>2*H14</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L14">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="M14">
-        <v>174</v>
+        <v>279</v>
       </c>
       <c r="N14">
         <v>2</v>
       </c>
       <c r="O14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P14">
-        <f>L14-M14</f>
-        <v>752</v>
+        <f t="shared" si="2"/>
+        <v>663</v>
       </c>
       <c r="Q14">
-        <f>O14+N14</f>
-        <v>12</v>
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="S14">
-        <f>(I14/10^3)/($AD$3*C14)</f>
-        <v>1.259185036740147E-5</v>
+        <f t="shared" si="4"/>
+        <v>1.2600451739599601E-5</v>
       </c>
       <c r="T14">
-        <f>S14*SQRT((J14/I14)^2+(D14/C14)^2+($AE$3/$AD$3)^2)</f>
-        <v>5.5104251991726919E-8</v>
+        <f t="shared" si="5"/>
+        <v>5.5302786380944353E-8</v>
       </c>
       <c r="U14">
-        <f>S14/($Z$3/10^6)</f>
-        <v>2.9980596112860643E-3</v>
+        <f t="shared" si="6"/>
+        <v>3.0001075570475241E-3</v>
       </c>
       <c r="V14">
-        <f>U14*SQRT((T14/S14)^2+($AA$3/$Z$3)^2)</f>
-        <v>7.2578088728497025E-5</v>
+        <f t="shared" si="7"/>
+        <v>7.2634600879331815E-5</v>
       </c>
       <c r="W14">
-        <f>P14/$AB$3</f>
-        <v>2.2719033232628401</v>
+        <f t="shared" si="8"/>
+        <v>2.0030211480362539</v>
       </c>
       <c r="X14">
-        <f>W14*SQRT((Q14/P14)^2+($AC$3/$AB$3)^2)</f>
-        <v>3.6415849479503985E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2457620102851751E-2</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>26</v>
-      </c>
       <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>29.9</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>0.1</v>
       </c>
-      <c r="F15">
-        <v>198</v>
-      </c>
-      <c r="G15">
-        <v>574</v>
-      </c>
       <c r="H15">
         <v>0.5</v>
       </c>
       <c r="I15">
-        <f>G15-F15</f>
-        <v>376</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J15">
-        <f>2*H15</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L15">
-        <v>942</v>
-      </c>
-      <c r="M15">
-        <v>279</v>
-      </c>
       <c r="N15">
         <v>2</v>
       </c>
@@ -1506,108 +1563,51 @@
         <v>2</v>
       </c>
       <c r="P15">
-        <f>L15-M15</f>
-        <v>663</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <f>O15+N15</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="S15">
-        <f>(I15/10^3)/($AD$3*C15)</f>
-        <v>1.2600451739599601E-5</v>
-      </c>
-      <c r="T15">
-        <f>S15*SQRT((J15/I15)^2+(D15/C15)^2+($AE$3/$AD$3)^2)</f>
-        <v>5.5302786380944353E-8</v>
-      </c>
-      <c r="U15">
-        <f>S15/($Z$3/10^6)</f>
-        <v>3.0001075570475241E-3</v>
-      </c>
-      <c r="V15">
-        <f>U15*SQRT((T15/S15)^2+($AA$3/$Z$3)^2)</f>
-        <v>7.2634600879331815E-5</v>
+      <c r="S15" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U15" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V15" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
       </c>
       <c r="W15">
-        <f>P15/$AB$3</f>
-        <v>2.0030211480362539</v>
-      </c>
-      <c r="X15">
-        <f>W15*SQRT((Q15/P15)^2+($AC$3/$AB$3)^2)</f>
-        <v>1.2457620102851751E-2</v>
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>0.1</v>
-      </c>
-      <c r="H16">
-        <v>0.5</v>
-      </c>
-      <c r="I16">
-        <f>G16-F16</f>
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <f>2*H16</f>
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>2</v>
-      </c>
-      <c r="O16">
-        <v>2</v>
-      </c>
-      <c r="P16">
-        <f>L16-M16</f>
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <f>O16+N16</f>
-        <v>4</v>
-      </c>
-      <c r="S16" t="e">
-        <f>(I16/10^3)/($AD$3*C16)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T16" t="e">
-        <f>S16*SQRT((J16/I16)^2+(D16/C16)^2+($AE$3/$AD$3)^2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U16" t="e">
-        <f>S16/($Z$3/10^6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V16" t="e">
-        <f>U16*SQRT((T16/S16)^2+($AA$3/$Z$3)^2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W16">
-        <f>P16/$AB$3</f>
-        <v>0</v>
-      </c>
-      <c r="X16" t="e">
-        <f>W16*SQRT((Q16/P16)^2+($AC$3/$AB$3)^2)</f>
-        <v>#DIV/0!</v>
+    <row r="18" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L18" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="12:19" x14ac:dyDescent="0.3">
-      <c r="L19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="12:19" x14ac:dyDescent="0.3">
-      <c r="S20" t="s">
+      <c r="S19" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:X16">
-    <sortCondition ref="A3:A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X15">
+    <sortCondition ref="A2:A15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/loi_darcy.xlsx
+++ b/loi_darcy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ABBA45-F481-4F33-B70B-4A86A9FEED7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A1A30-5D6D-46C6-83F6-65248240C855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1538,63 +1538,6 @@
         <v>1.2457620102851751E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <v>0.1</v>
-      </c>
-      <c r="H15">
-        <v>0.5</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>2</v>
-      </c>
-      <c r="O15">
-        <v>2</v>
-      </c>
-      <c r="P15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="S15" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T15" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U15" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V15" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W15">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="X15" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
     <row r="18" spans="12:19" x14ac:dyDescent="0.3">
       <c r="L18" t="s">
         <v>10</v>

--- a/loi_darcy.xlsx
+++ b/loi_darcy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5A1A30-5D6D-46C6-83F6-65248240C855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831BE7BD-B183-4239-86A5-8673658345C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/loi_darcy.xlsx
+++ b/loi_darcy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831BE7BD-B183-4239-86A5-8673658345C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E53C70-8741-4CEA-9C76-004388FBC78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,9 +99,6 @@
     <t>débit_(m^3/s)</t>
   </si>
   <si>
-    <t>flux_Darcy_(m/s)</t>
-  </si>
-  <si>
     <t>vitesse</t>
   </si>
   <si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>tare_(g)</t>
+  </si>
+  <si>
+    <t>flux_Darcy_(mm/s)</t>
   </si>
 </sst>
 </file>
@@ -144,11 +144,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AE20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="7.5546875" customWidth="1"/>
@@ -448,7 +449,7 @@
     <col min="18" max="18" width="2.109375" customWidth="1"/>
     <col min="19" max="19" width="12.5546875" customWidth="1"/>
     <col min="20" max="20" width="10.109375" customWidth="1"/>
-    <col min="21" max="21" width="14.88671875" customWidth="1"/>
+    <col min="21" max="21" width="16.6640625" customWidth="1"/>
     <col min="22" max="22" width="8.33203125" customWidth="1"/>
     <col min="23" max="23" width="7.44140625" customWidth="1"/>
     <col min="24" max="24" width="7.77734375" customWidth="1"/>
@@ -463,7 +464,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -475,7 +476,7 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
         <v>18</v>
@@ -499,7 +500,7 @@
         <v>22</v>
       </c>
       <c r="O1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P1" t="s">
         <v>11</v>
@@ -515,7 +516,7 @@
         <v>4</v>
       </c>
       <c r="U1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>5</v>
@@ -568,11 +569,11 @@
         <v>0.5</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I15" si="0">G2-F2</f>
+        <f t="shared" ref="I2:I14" si="0">G2-F2</f>
         <v>75.5</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J15" si="1">2*H2</f>
+        <f t="shared" ref="J2:J14" si="1">2*H2</f>
         <v>1</v>
       </c>
       <c r="L2">
@@ -588,35 +589,35 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P15" si="2">L2-M2</f>
+        <f t="shared" ref="P2:P14" si="2">L2-M2</f>
         <v>145</v>
       </c>
       <c r="Q2">
-        <f t="shared" ref="Q2:Q15" si="3">O2+N2</f>
+        <f t="shared" ref="Q2:Q14" si="3">O2+N2</f>
         <v>4</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:S15" si="4">(I2/10^3)/($AD$2*C2)</f>
+        <f>(I2/10^3)/($AD$2*C2)</f>
         <v>2.5050100200400804E-6</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T15" si="5">S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
+        <f>S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
         <v>3.4292054268838759E-8</v>
       </c>
       <c r="U2">
-        <f t="shared" ref="U2:U15" si="6">S2/($Z$2/10^6)</f>
-        <v>5.964309571524001E-4</v>
+        <f>S2/($Z$2/10^6)*10^3</f>
+        <v>0.59643095715240013</v>
       </c>
       <c r="V2">
-        <f t="shared" ref="V2:V15" si="7">U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
-        <v>1.6380612974879218E-5</v>
-      </c>
-      <c r="W2">
-        <f t="shared" ref="W2:W15" si="8">P2/$AB$2</f>
+        <f>U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
+        <v>1.6380612974879218E-2</v>
+      </c>
+      <c r="W2" s="2">
+        <f t="shared" ref="W2:W14" si="4">P2/$AB$2</f>
         <v>0.4380664652567976</v>
       </c>
       <c r="X2">
-        <f t="shared" ref="X2:X15" si="9">W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
+        <f>W2*SQRT((Q2/P2)^2+($AC$2/$AB$2)^2)</f>
         <v>1.2102696241490761E-2</v>
       </c>
       <c r="Z2">
@@ -689,27 +690,27 @@
         <v>4</v>
       </c>
       <c r="S3">
+        <f t="shared" ref="S3:S14" si="5">(I3/10^3)/($AD$2*C3)</f>
+        <v>3.406813627254509E-6</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T14" si="6">S3*SQRT((J3/I3)^2+(D3/C3)^2+($AE$2/$AD$2)^2)</f>
+        <v>3.5442652785390082E-8</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U14" si="7">S3/($Z$2/10^6)*10^3</f>
+        <v>0.81114610172726409</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V14" si="8">U3*SQRT((T3/S3)^2+($AA$2/$Z$2)^2)</f>
+        <v>2.1076151770803291E-2</v>
+      </c>
+      <c r="W3" s="2">
         <f t="shared" si="4"/>
-        <v>3.406813627254509E-6</v>
-      </c>
-      <c r="T3">
-        <f t="shared" si="5"/>
-        <v>3.5442652785390082E-8</v>
-      </c>
-      <c r="U3">
-        <f t="shared" si="6"/>
-        <v>8.1114610172726409E-4</v>
-      </c>
-      <c r="V3">
-        <f t="shared" si="7"/>
-        <v>2.1076151770803291E-5</v>
-      </c>
-      <c r="W3">
-        <f t="shared" si="8"/>
         <v>0.55287009063444104</v>
       </c>
       <c r="X3">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="X3:X14" si="9">W3*SQRT((Q3/P3)^2+($AC$2/$AB$2)^2)</f>
         <v>1.2113415902573529E-2</v>
       </c>
     </row>
@@ -764,23 +765,23 @@
         <v>4</v>
       </c>
       <c r="S4">
+        <f t="shared" si="5"/>
+        <v>4.121956287156253E-6</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="6"/>
+        <v>3.6471229298589113E-8</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="7"/>
+        <v>0.98141816360863177</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="8"/>
+        <v>2.4928431214823365E-2</v>
+      </c>
+      <c r="W4" s="2">
         <f t="shared" si="4"/>
-        <v>4.121956287156253E-6</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="5"/>
-        <v>3.6471229298589113E-8</v>
-      </c>
-      <c r="U4">
-        <f t="shared" si="6"/>
-        <v>9.8141816360863181E-4</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="7"/>
-        <v>2.4928431214823366E-5</v>
-      </c>
-      <c r="W4">
-        <f t="shared" si="8"/>
         <v>0.68277945619335345</v>
       </c>
       <c r="X4">
@@ -839,23 +840,23 @@
         <v>4</v>
       </c>
       <c r="S5">
+        <f t="shared" si="5"/>
+        <v>4.7428189712758846E-6</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="6"/>
+        <v>3.7257086899611824E-8</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="7"/>
+        <v>1.1292426122085439</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="8"/>
+        <v>2.8312296408463423E-2</v>
+      </c>
+      <c r="W5" s="2">
         <f t="shared" si="4"/>
-        <v>4.7428189712758846E-6</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="5"/>
-        <v>3.7257086899611824E-8</v>
-      </c>
-      <c r="U5">
-        <f t="shared" si="6"/>
-        <v>1.129242612208544E-3</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="7"/>
-        <v>2.8312296408463423E-5</v>
-      </c>
-      <c r="W5">
-        <f t="shared" si="8"/>
         <v>0.77039274924471302</v>
       </c>
       <c r="X5">
@@ -914,23 +915,23 @@
         <v>4</v>
       </c>
       <c r="S6">
+        <f t="shared" si="5"/>
+        <v>5.3429117370954528E-6</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="6"/>
+        <v>3.810395820831726E-8</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="7"/>
+        <v>1.272121842165584</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="8"/>
+        <v>3.1618161422865852E-2</v>
+      </c>
+      <c r="W6" s="2">
         <f t="shared" si="4"/>
-        <v>5.3429117370954528E-6</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="5"/>
-        <v>3.810395820831726E-8</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="6"/>
-        <v>1.272121842165584E-3</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="7"/>
-        <v>3.1618161422865852E-5</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="8"/>
         <v>0.8821752265861027</v>
       </c>
       <c r="X6">
@@ -989,23 +990,23 @@
         <v>6</v>
       </c>
       <c r="S7">
+        <f t="shared" si="5"/>
+        <v>6.6245447706043312E-6</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="6"/>
+        <v>4.0454932254959881E-8</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="7"/>
+        <v>1.5772725644296026</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="8"/>
+        <v>3.8769691046076256E-2</v>
+      </c>
+      <c r="W7" s="2">
         <f t="shared" si="4"/>
-        <v>6.6245447706043312E-6</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="5"/>
-        <v>4.0454932254959881E-8</v>
-      </c>
-      <c r="U7">
-        <f t="shared" si="6"/>
-        <v>1.5772725644296027E-3</v>
-      </c>
-      <c r="V7">
-        <f t="shared" si="7"/>
-        <v>3.8769691046076259E-5</v>
-      </c>
-      <c r="W7">
-        <f t="shared" si="8"/>
         <v>1.1057401812688821</v>
       </c>
       <c r="X7">
@@ -1064,23 +1065,23 @@
         <v>4</v>
       </c>
       <c r="S8">
+        <f t="shared" si="5"/>
+        <v>7.3901956737395054E-6</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="6"/>
+        <v>4.2021551106583754E-8</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="7"/>
+        <v>1.759570398509406</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="8"/>
+        <v>4.3072666168818913E-2</v>
+      </c>
+      <c r="W8" s="2">
         <f t="shared" si="4"/>
-        <v>7.3901956737395054E-6</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="5"/>
-        <v>4.2021551106583754E-8</v>
-      </c>
-      <c r="U8">
-        <f t="shared" si="6"/>
-        <v>1.759570398509406E-3</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="7"/>
-        <v>4.307266616881891E-5</v>
-      </c>
-      <c r="W8">
-        <f t="shared" si="8"/>
         <v>1.6978851963746224</v>
       </c>
       <c r="X8">
@@ -1139,23 +1140,23 @@
         <v>5</v>
       </c>
       <c r="S9">
+        <f t="shared" si="5"/>
+        <v>8.0093296961816622E-6</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="6"/>
+        <v>4.364626552580502E-8</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="7"/>
+        <v>1.9069832609956339</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="8"/>
+        <v>4.6578420007594531E-2</v>
+      </c>
+      <c r="W9" s="2">
         <f t="shared" si="4"/>
-        <v>8.0093296961816622E-6</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="5"/>
-        <v>4.364626552580502E-8</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="6"/>
-        <v>1.9069832609956339E-3</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="7"/>
-        <v>4.6578420007594534E-5</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="8"/>
         <v>1.3293051359516617</v>
       </c>
       <c r="X9">
@@ -1214,23 +1215,23 @@
         <v>4</v>
       </c>
       <c r="S10">
+        <f t="shared" si="5"/>
+        <v>8.7842351369405489E-6</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="6"/>
+        <v>4.5281404465810625E-8</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="7"/>
+        <v>2.0914845564144167</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="8"/>
+        <v>5.0950980225292666E-2</v>
+      </c>
+      <c r="W10" s="2">
         <f t="shared" si="4"/>
-        <v>8.7842351369405489E-6</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="5"/>
-        <v>4.5281404465810625E-8</v>
-      </c>
-      <c r="U10">
-        <f t="shared" si="6"/>
-        <v>2.0914845564144165E-3</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="7"/>
-        <v>5.0950980225292664E-5</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="8"/>
         <v>1.9214501510574018</v>
       </c>
       <c r="X10">
@@ -1289,23 +1290,23 @@
         <v>8</v>
       </c>
       <c r="S11">
+        <f t="shared" si="5"/>
+        <v>1.0204355198691699E-5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="6"/>
+        <v>4.8911444595405938E-8</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="7"/>
+        <v>2.4296083806408806</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="8"/>
+        <v>5.9008386661903181E-2</v>
+      </c>
+      <c r="W11" s="2">
         <f t="shared" si="4"/>
-        <v>1.0204355198691699E-5</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="5"/>
-        <v>4.8911444595405938E-8</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="6"/>
-        <v>2.4296083806408806E-3</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="7"/>
-        <v>5.9008386661903181E-5</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="8"/>
         <v>1.7401812688821752</v>
       </c>
       <c r="X11">
@@ -1364,23 +1365,23 @@
         <v>4</v>
       </c>
       <c r="S12">
+        <f t="shared" si="5"/>
+        <v>1.1173663115705097E-5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="6"/>
+        <v>5.0623327338103899E-8</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="7"/>
+        <v>2.6603959799297852</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="8"/>
+        <v>6.4479333191259661E-2</v>
+      </c>
+      <c r="W12" s="2">
         <f t="shared" si="4"/>
-        <v>1.1173663115705097E-5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="5"/>
-        <v>5.0623327338103899E-8</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="6"/>
-        <v>2.6603959799297852E-3</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="7"/>
-        <v>6.4479333191259661E-5</v>
-      </c>
-      <c r="W12">
-        <f t="shared" si="8"/>
         <v>1.8006042296072509</v>
       </c>
       <c r="X12">
@@ -1439,23 +1440,23 @@
         <v>12</v>
       </c>
       <c r="S13">
+        <f t="shared" si="5"/>
+        <v>1.259185036740147E-5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="6"/>
+        <v>5.5104251991726919E-8</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="7"/>
+        <v>2.9980596112860645</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="8"/>
+        <v>7.2578088728497026E-2</v>
+      </c>
+      <c r="W13" s="2">
         <f t="shared" si="4"/>
-        <v>1.259185036740147E-5</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="5"/>
-        <v>5.5104251991726919E-8</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="6"/>
-        <v>2.9980596112860643E-3</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="7"/>
-        <v>7.2578088728497025E-5</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="8"/>
         <v>2.2719033232628401</v>
       </c>
       <c r="X13">
@@ -1514,23 +1515,23 @@
         <v>4</v>
       </c>
       <c r="S14">
+        <f t="shared" si="5"/>
+        <v>1.2600451739599601E-5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="6"/>
+        <v>5.5302786380944353E-8</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="7"/>
+        <v>3.000107557047524</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="8"/>
+        <v>7.2634600879331809E-2</v>
+      </c>
+      <c r="W14" s="2">
         <f t="shared" si="4"/>
-        <v>1.2600451739599601E-5</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="5"/>
-        <v>5.5302786380944353E-8</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="6"/>
-        <v>3.0001075570475241E-3</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="7"/>
-        <v>7.2634600879331815E-5</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="8"/>
         <v>2.0030211480362539</v>
       </c>
       <c r="X14">
@@ -1538,14 +1539,19 @@
         <v>1.2457620102851751E-2</v>
       </c>
     </row>
-    <row r="18" spans="12:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="12:27" x14ac:dyDescent="0.3">
       <c r="L18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="12:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:27" x14ac:dyDescent="0.3">
       <c r="S19" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="12:27" x14ac:dyDescent="0.3">
+      <c r="AA20">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/loi_darcy.xlsx
+++ b/loi_darcy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas Onillon\Documents\UNINe\géologie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E53C70-8741-4CEA-9C76-004388FBC78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{872FF1C1-119D-4F49-ADB1-9BA3ECA809D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,11 +569,10 @@
         <v>0.5</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I14" si="0">G2-F2</f>
-        <v>75.5</v>
+        <v>75</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J14" si="1">2*H2</f>
+        <f t="shared" ref="J2:J14" si="0">2*H2</f>
         <v>1</v>
       </c>
       <c r="L2">
@@ -589,31 +588,31 @@
         <v>2</v>
       </c>
       <c r="P2">
-        <f t="shared" ref="P2:P14" si="2">L2-M2</f>
+        <f t="shared" ref="P2:P14" si="1">L2-M2</f>
         <v>145</v>
       </c>
       <c r="Q2">
-        <f t="shared" ref="Q2:Q14" si="3">O2+N2</f>
+        <f t="shared" ref="Q2:Q14" si="2">O2+N2</f>
         <v>4</v>
       </c>
       <c r="S2">
         <f>(I2/10^3)/($AD$2*C2)</f>
-        <v>2.5050100200400804E-6</v>
+        <v>2.4884205497086888E-6</v>
       </c>
       <c r="T2">
         <f>S2*SQRT((J2/I2)^2+(D2/C2)^2+($AE$2/$AD$2)^2)</f>
-        <v>3.4292054268838759E-8</v>
+        <v>3.4277595301499635E-8</v>
       </c>
       <c r="U2">
         <f>S2/($Z$2/10^6)*10^3</f>
-        <v>0.59643095715240013</v>
-      </c>
-      <c r="V2">
+        <v>0.59248108326397353</v>
+      </c>
+      <c r="V2" s="2">
         <f>U2*SQRT((T2/S2)^2+($AA$2/$Z$2)^2)</f>
-        <v>1.6380612974879218E-2</v>
+        <v>2.2679386693545803E-2</v>
       </c>
       <c r="W2" s="2">
-        <f t="shared" ref="W2:W14" si="4">P2/$AB$2</f>
+        <f t="shared" ref="W2:W14" si="3">P2/$AB$2</f>
         <v>0.4380664652567976</v>
       </c>
       <c r="X2">
@@ -624,7 +623,7 @@
         <v>4200</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AB2">
         <v>331</v>
@@ -662,11 +661,11 @@
         <v>0.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I2:I14" si="4">G3-F3</f>
+        <v>102</v>
+      </c>
+      <c r="J3">
         <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-      <c r="J3">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L3">
@@ -682,11 +681,11 @@
         <v>2</v>
       </c>
       <c r="P3">
+        <f t="shared" si="1"/>
+        <v>183</v>
+      </c>
+      <c r="Q3">
         <f t="shared" si="2"/>
-        <v>183</v>
-      </c>
-      <c r="Q3">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S3">
@@ -701,12 +700,12 @@
         <f t="shared" ref="U3:U14" si="7">S3/($Z$2/10^6)*10^3</f>
         <v>0.81114610172726409</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="2">
         <f t="shared" ref="V3:V14" si="8">U3*SQRT((T3/S3)^2+($AA$2/$Z$2)^2)</f>
-        <v>2.1076151770803291E-2</v>
+        <v>3.0173568759096249E-2</v>
       </c>
       <c r="W3" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.55287009063444104</v>
       </c>
       <c r="X3">
@@ -737,11 +736,11 @@
         <v>0.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="4"/>
+        <v>123</v>
+      </c>
+      <c r="J4">
         <f t="shared" si="0"/>
-        <v>123</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L4">
@@ -757,11 +756,11 @@
         <v>2</v>
       </c>
       <c r="P4">
+        <f t="shared" si="1"/>
+        <v>226</v>
+      </c>
+      <c r="Q4">
         <f t="shared" si="2"/>
-        <v>226</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S4">
@@ -776,12 +775,12 @@
         <f t="shared" si="7"/>
         <v>0.98141816360863177</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="2">
         <f t="shared" si="8"/>
-        <v>2.4928431214823365E-2</v>
+        <v>3.611029403408355E-2</v>
       </c>
       <c r="W4" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.68277945619335345</v>
       </c>
       <c r="X4">
@@ -812,11 +811,11 @@
         <v>0.5</v>
       </c>
       <c r="I5">
+        <f t="shared" si="4"/>
+        <v>142</v>
+      </c>
+      <c r="J5">
         <f t="shared" si="0"/>
-        <v>142</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L5">
@@ -832,11 +831,11 @@
         <v>2</v>
       </c>
       <c r="P5">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="Q5">
         <f t="shared" si="2"/>
-        <v>255</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S5">
@@ -851,12 +850,12 @@
         <f t="shared" si="7"/>
         <v>1.1292426122085439</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="2">
         <f t="shared" si="8"/>
-        <v>2.8312296408463423E-2</v>
+        <v>4.1294144428131001E-2</v>
       </c>
       <c r="W5" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.77039274924471302</v>
       </c>
       <c r="X5">
@@ -887,11 +886,10 @@
         <v>0.5</v>
       </c>
       <c r="I6">
+        <v>160</v>
+      </c>
+      <c r="J6">
         <f t="shared" si="0"/>
-        <v>160.5</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L6">
@@ -907,31 +905,31 @@
         <v>2</v>
       </c>
       <c r="P6">
+        <f t="shared" si="1"/>
+        <v>292</v>
+      </c>
+      <c r="Q6">
         <f t="shared" si="2"/>
-        <v>292</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S6">
         <f t="shared" si="5"/>
-        <v>5.3429117370954528E-6</v>
+        <v>5.3262671522446879E-6</v>
       </c>
       <c r="T6">
         <f t="shared" si="6"/>
-        <v>3.810395820831726E-8</v>
+        <v>3.8075888267519184E-8</v>
       </c>
       <c r="U6">
         <f t="shared" si="7"/>
-        <v>1.272121842165584</v>
-      </c>
-      <c r="V6">
+        <v>1.2681588457725448</v>
+      </c>
+      <c r="V6" s="2">
         <f t="shared" si="8"/>
-        <v>3.1618161422865852E-2</v>
+        <v>4.6189787411937196E-2</v>
       </c>
       <c r="W6" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.8821752265861027</v>
       </c>
       <c r="X6">
@@ -962,11 +960,11 @@
         <v>0.5</v>
       </c>
       <c r="I7">
+        <f t="shared" si="4"/>
+        <v>199</v>
+      </c>
+      <c r="J7">
         <f t="shared" si="0"/>
-        <v>199</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L7">
@@ -982,11 +980,11 @@
         <v>4</v>
       </c>
       <c r="P7">
+        <f t="shared" si="1"/>
+        <v>366</v>
+      </c>
+      <c r="Q7">
         <f t="shared" si="2"/>
-        <v>366</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="S7">
@@ -1001,12 +999,12 @@
         <f t="shared" si="7"/>
         <v>1.5772725644296026</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="2">
         <f t="shared" si="8"/>
-        <v>3.8769691046076256E-2</v>
+        <v>5.7148733948822382E-2</v>
       </c>
       <c r="W7" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.1057401812688821</v>
       </c>
       <c r="X7">
@@ -1037,11 +1035,11 @@
         <v>0.5</v>
       </c>
       <c r="I8">
+        <f t="shared" si="4"/>
+        <v>222</v>
+      </c>
+      <c r="J8">
         <f t="shared" si="0"/>
-        <v>222</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L8">
@@ -1057,11 +1055,11 @@
         <v>2</v>
       </c>
       <c r="P8">
+        <f t="shared" si="1"/>
+        <v>562</v>
+      </c>
+      <c r="Q8">
         <f t="shared" si="2"/>
-        <v>562</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S8">
@@ -1076,12 +1074,12 @@
         <f t="shared" si="7"/>
         <v>1.759570398509406</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="2">
         <f t="shared" si="8"/>
-        <v>4.3072666168818913E-2</v>
+        <v>6.3633281160062866E-2</v>
       </c>
       <c r="W8" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6978851963746224</v>
       </c>
       <c r="X8">
@@ -1112,11 +1110,11 @@
         <v>0.5</v>
       </c>
       <c r="I9">
+        <f t="shared" si="4"/>
+        <v>239</v>
+      </c>
+      <c r="J9">
         <f t="shared" si="0"/>
-        <v>239</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L9">
@@ -1132,11 +1130,11 @@
         <v>3</v>
       </c>
       <c r="P9">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="Q9">
         <f t="shared" si="2"/>
-        <v>440</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="S9">
@@ -1151,12 +1149,12 @@
         <f t="shared" si="7"/>
         <v>1.9069832609956339</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="2">
         <f t="shared" si="8"/>
-        <v>4.6578420007594531E-2</v>
+        <v>6.889480731685374E-2</v>
       </c>
       <c r="W9" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.3293051359516617</v>
       </c>
       <c r="X9">
@@ -1187,11 +1185,11 @@
         <v>0.5</v>
       </c>
       <c r="I10">
+        <f t="shared" si="4"/>
+        <v>263</v>
+      </c>
+      <c r="J10">
         <f t="shared" si="0"/>
-        <v>263</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L10">
@@ -1207,11 +1205,11 @@
         <v>2</v>
       </c>
       <c r="P10">
+        <f t="shared" si="1"/>
+        <v>636</v>
+      </c>
+      <c r="Q10">
         <f t="shared" si="2"/>
-        <v>636</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S10">
@@ -1226,12 +1224,12 @@
         <f t="shared" si="7"/>
         <v>2.0914845564144167</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="2">
         <f t="shared" si="8"/>
-        <v>5.0950980225292666E-2</v>
+        <v>7.5469929028656887E-2</v>
       </c>
       <c r="W10" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.9214501510574018</v>
       </c>
       <c r="X10">
@@ -1262,11 +1260,10 @@
         <v>0.5</v>
       </c>
       <c r="I11">
+        <v>304</v>
+      </c>
+      <c r="J11">
         <f t="shared" si="0"/>
-        <v>304.5</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L11">
@@ -1282,31 +1279,31 @@
         <v>6</v>
       </c>
       <c r="P11">
+        <f t="shared" si="1"/>
+        <v>576</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>576</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="S11">
         <f t="shared" si="5"/>
-        <v>1.0204355198691699E-5</v>
+        <v>1.0187599278825209E-5</v>
       </c>
       <c r="T11">
         <f t="shared" si="6"/>
-        <v>4.8911444595405938E-8</v>
+        <v>4.8868849053365915E-8</v>
       </c>
       <c r="U11">
         <f t="shared" si="7"/>
-        <v>2.4296083806408806</v>
-      </c>
-      <c r="V11">
+        <v>2.425618875910764</v>
+      </c>
+      <c r="V11" s="2">
         <f t="shared" si="8"/>
-        <v>5.9008386661903181E-2</v>
+        <v>8.7407148778304578E-2</v>
       </c>
       <c r="W11" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.7401812688821752</v>
       </c>
       <c r="X11">
@@ -1337,11 +1334,11 @@
         <v>0.5</v>
       </c>
       <c r="I12">
+        <f t="shared" si="4"/>
+        <v>339</v>
+      </c>
+      <c r="J12">
         <f t="shared" si="0"/>
-        <v>339</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L12">
@@ -1357,11 +1354,11 @@
         <v>2</v>
       </c>
       <c r="P12">
+        <f t="shared" si="1"/>
+        <v>596</v>
+      </c>
+      <c r="Q12">
         <f t="shared" si="2"/>
-        <v>596</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S12">
@@ -1376,12 +1373,12 @@
         <f t="shared" si="7"/>
         <v>2.6603959799297852</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="2">
         <f t="shared" si="8"/>
-        <v>6.4479333191259661E-2</v>
+        <v>9.5775603314575297E-2</v>
       </c>
       <c r="W12" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.8006042296072509</v>
       </c>
       <c r="X12">
@@ -1412,11 +1409,11 @@
         <v>0.5</v>
       </c>
       <c r="I13">
+        <f t="shared" si="4"/>
+        <v>377</v>
+      </c>
+      <c r="J13">
         <f t="shared" si="0"/>
-        <v>377</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L13">
@@ -1432,11 +1429,11 @@
         <v>10</v>
       </c>
       <c r="P13">
+        <f t="shared" si="1"/>
+        <v>752</v>
+      </c>
+      <c r="Q13">
         <f t="shared" si="2"/>
-        <v>752</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="S13">
@@ -1451,12 +1448,12 @@
         <f t="shared" si="7"/>
         <v>2.9980596112860645</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="2">
         <f t="shared" si="8"/>
-        <v>7.2578088728497026E-2</v>
+        <v>0.10787438389114294</v>
       </c>
       <c r="W13" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.2719033232628401</v>
       </c>
       <c r="X13">
@@ -1487,11 +1484,11 @@
         <v>0.5</v>
       </c>
       <c r="I14">
+        <f t="shared" si="4"/>
+        <v>376</v>
+      </c>
+      <c r="J14">
         <f t="shared" si="0"/>
-        <v>376</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L14">
@@ -1507,11 +1504,11 @@
         <v>2</v>
       </c>
       <c r="P14">
+        <f t="shared" si="1"/>
+        <v>663</v>
+      </c>
+      <c r="Q14">
         <f t="shared" si="2"/>
-        <v>663</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="S14">
@@ -1526,12 +1523,12 @@
         <f t="shared" si="7"/>
         <v>3.000107557047524</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="2">
         <f t="shared" si="8"/>
-        <v>7.2634600879331809E-2</v>
+        <v>0.10795273768588626</v>
       </c>
       <c r="W14" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.0030211480362539</v>
       </c>
       <c r="X14">
